--- a/data/04_extraction/AI_Adoption_MASEM_Coding_v2.xlsx
+++ b/data/04_extraction/AI_Adoption_MASEM_Coding_v2.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,6 +47,11 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font/>
+    <font>
+      <b val="1"/>
+      <color rgb="002F5496"/>
     </font>
   </fonts>
   <fills count="4">
@@ -95,13 +100,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -467,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1467,265 +1477,257 @@
       <c r="G31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>— STUDY_METADATA: Coding Workflow (2-Pair Design) —</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>coding_phase</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>STUDY_METADATA</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>calibration, phase1_dual, phase2_single</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Phase of coding workflow: calibration (10 studies, all 4 coders), phase1_dual (100 studies, 2-pair independent), phase2_single (~150 studies, single coder + spot-check)</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>phase1_dual</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Determines coder assignment pattern</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>coder_pair</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>STUDY_METADATA</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>pair_A, pair_B, NA</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>Coder pair assignment for Phase 1: pair_A (R1+R2), pair_B (R3+R4), NA for Phase 2</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>pair_A</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>Only applicable in phase1_dual; NA for calibration and phase2_single</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>primary_coder</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>STUDY_METADATA</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>R1, R2, R3, R4</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Primary coder who coded this study</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>All phases; in dual coding, both coders code independently</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>secondary_coder</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>STUDY_METADATA</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>R1, R2, R3, R4, NA</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>Second independent coder (Phase 1 dual coding only)</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>NA for phase2_single; in calibration all 4 coders code</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>spot_checker</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>STUDY_METADATA</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>R1, R2, R3, R4, NA</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Coder who spot-checked this study (Phase 2, 15-20% sample)</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>NA unless phase2_single and selected for spot-check</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>adjudicator</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>STUDY_METADATA</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>R1, R2, R3, R4, NA</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>Coder who resolved discrepancies (cross-pair: Pair A discrepancies adjudicated by R3/R4, Pair B by R1/R2)</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>Cross-pair adjudication ensures independence; NA if no discrepancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>— CORRELATION_MATRIX —</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr"/>
-      <c r="C32" s="2" t="inlineStr"/>
-      <c r="D32" s="2" t="inlineStr"/>
-      <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>study_id</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>CORRELATION_MATRIX</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>S###</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>Links to STUDY_METADATA</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>S001</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>construct_row</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>CORRELATION_MATRIX</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>categorical</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>PE,EE,SI,FC,BI,UB,ATT,SE,TRU,ANX,TRA,AUT</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>Row construct</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>PE</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>12 target constructs</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>construct_col</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>CORRELATION_MATRIX</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>categorical</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>PE,EE,SI,FC,BI,UB,ATT,SE,TRU,ANX,TRA,AUT</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>Column construct</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>BI</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>12 target constructs</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>r_value</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>CORRELATION_MATRIX</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>-1 to 1</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>Pearson correlation coefficient</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>2 decimal places</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>r_source</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>CORRELATION_MATRIX</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>categorical</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>direct, beta_converted, author_provided</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>Source of r value</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>original_beta</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>CORRELATION_MATRIX</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>-1 to 1 or NA</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>Original β if r_source=beta_converted</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>r_sample_size</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>CORRELATION_MATRIX</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>≥50 or NA</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>Pairwise N if different from study N</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr"/>
+      <c r="B39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n"/>
+      <c r="E39" s="2" t="n"/>
+      <c r="F39" s="2" t="n"/>
+      <c r="G39" s="2" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>p_value</t>
+          <t>study_id</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -1735,30 +1737,30 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>0-1 or NA</t>
+          <t>S###</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Reported p-value</t>
+          <t>Links to STUDY_METADATA</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>0.001</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr"/>
+          <t>S001</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>significance</t>
+          <t>construct_row</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -1773,25 +1775,29 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>p&lt;.001, p&lt;.01, p&lt;.05, ns, NR</t>
+          <t>PE,EE,SI,FC,BI,UB,ATT,SE,TRU,ANX,TRA,AUT</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Significance level</t>
+          <t>Row construct</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>p&lt;.001</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr"/>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>12 target constructs</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>source_location</t>
+          <t>construct_col</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -1801,30 +1807,34 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>categorical</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>free text</t>
+          <t>PE,EE,SI,FC,BI,UB,ATT,SE,TRU,ANX,TRA,AUT</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Location in paper</t>
+          <t>Column construct</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Table 3</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="inlineStr"/>
+          <t>BI</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>12 target constructs</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>extraction_notes</t>
+          <t>r_value</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -1834,147 +1844,171 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>free text</t>
+          <t>-1 to 1</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Extraction notes</t>
+          <t>Pearson correlation coefficient</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>Lower triangle only</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr"/>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>2 decimal places</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>— CONSTRUCT_MAPPING —</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr"/>
-      <c r="C44" s="2" t="inlineStr"/>
-      <c r="D44" s="2" t="inlineStr"/>
-      <c r="E44" s="2" t="inlineStr"/>
-      <c r="F44" s="2" t="inlineStr"/>
-      <c r="G44" s="2" t="inlineStr"/>
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>r_source</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>CORRELATION_MATRIX</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>direct, beta_converted, author_provided</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Source of r value</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>study_id</t>
+          <t>original_beta</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>CONSTRUCT_MAPPING</t>
+          <t>CORRELATION_MATRIX</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>S###</t>
+          <t>-1 to 1 or NA</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Links to STUDY_METADATA</t>
+          <t>Original β if r_source=beta_converted</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>S001</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr"/>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>study_construct_label</t>
+          <t>r_sample_size</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>CONSTRUCT_MAPPING</t>
+          <t>CORRELATION_MATRIX</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>free text</t>
+          <t>≥50 or NA</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Original label in study</t>
+          <t>Pairwise N if different from study N</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Perceived Usefulness</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr"/>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>standard_construct</t>
+          <t>p_value</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>CONSTRUCT_MAPPING</t>
+          <t>CORRELATION_MATRIX</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>categorical</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>PE,EE,SI,FC,BI,UB,ATT,SE,TRU,ANX,TRA,AUT</t>
+          <t>0-1 or NA</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Mapped to which standard construct</t>
+          <t>Reported p-value</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>PE</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr"/>
+          <t>0.001</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>confidence</t>
+          <t>significance</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>CONSTRUCT_MAPPING</t>
+          <t>CORRELATION_MATRIX</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -1984,34 +2018,30 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>exact, high, moderate, low</t>
+          <t>p&lt;.001, p&lt;.01, p&lt;.05, ns, NR</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Mapping confidence level</t>
+          <t>Significance level</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="G48" s="3" t="inlineStr">
-        <is>
-          <t>See §7.4 decision tree</t>
-        </is>
-      </c>
+          <t>p&lt;.001</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>mapping_rationale</t>
+          <t>source_location</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>CONSTRUCT_MAPPING</t>
+          <t>CORRELATION_MATRIX</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -2026,90 +2056,66 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Rationale for mapping decision</t>
+          <t>Location in paper</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>TAM PU = UTAUT PE</t>
-        </is>
-      </c>
-      <c r="G49" s="3" t="inlineStr"/>
+          <t>Table 3</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>model_origin</t>
+          <t>extraction_notes</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>CONSTRUCT_MAPPING</t>
+          <t>CORRELATION_MATRIX</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>categorical</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>TAM, UTAUT, UTAUT2, TPB, SCT, DOI, AI_specific, other</t>
+          <t>free text</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Theoretical origin of study construct</t>
+          <t>Extraction notes</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>TAM</t>
-        </is>
-      </c>
-      <c r="G50" s="3" t="inlineStr"/>
+          <t>Lower triangle only</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>reverse_coded</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>CONSTRUCT_MAPPING</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>TRUE, FALSE</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>Whether sign was reversed</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="G51" s="3" t="inlineStr">
-        <is>
-          <t>e.g., Complexity → EE (reverse)</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>— CONSTRUCT_MAPPING —</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="n"/>
+      <c r="E51" s="2" t="n"/>
+      <c r="F51" s="2" t="n"/>
+      <c r="G51" s="2" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>n_items</t>
+          <t>study_id</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -2119,30 +2125,30 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>≥1</t>
+          <t>S###</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Number of items in scale</t>
+          <t>Links to STUDY_METADATA</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G52" s="3" t="inlineStr"/>
+          <t>S001</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>scale_source</t>
+          <t>study_construct_label</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -2162,20 +2168,20 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Citation for scale</t>
+          <t>Original label in study</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>Venkatesh et al. (2003)</t>
-        </is>
-      </c>
-      <c r="G53" s="3" t="inlineStr"/>
+          <t>Perceived Usefulness</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>items_reviewed</t>
+          <t>standard_construct</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -2185,52 +2191,72 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>categorical</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>TRUE, FALSE</t>
+          <t>PE,EE,SI,FC,BI,UB,ATT,SE,TRU,ANX,TRA,AUT</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Whether items were reviewed for mapping</t>
+          <t>Mapped to which standard construct</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="G54" s="3" t="inlineStr">
-        <is>
-          <t>Required if confidence=moderate/low</t>
-        </is>
-      </c>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>— MODERATOR_VARIABLES —</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr"/>
-      <c r="C55" s="2" t="inlineStr"/>
-      <c r="D55" s="2" t="inlineStr"/>
-      <c r="E55" s="2" t="inlineStr"/>
-      <c r="F55" s="2" t="inlineStr"/>
-      <c r="G55" s="2" t="inlineStr"/>
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>confidence</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>CONSTRUCT_MAPPING</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>exact, high, moderate, low</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Mapping confidence level</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>See §7.4 decision tree</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>study_id</t>
+          <t>mapping_rationale</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>MODERATOR_VARIABLES</t>
+          <t>CONSTRUCT_MAPPING</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -2240,30 +2266,30 @@
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>S###</t>
+          <t>free text</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Links to STUDY_METADATA</t>
+          <t>Rationale for mapping decision</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>S001</t>
-        </is>
-      </c>
-      <c r="G56" s="3" t="inlineStr"/>
+          <t>TAM PU = UTAUT PE</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>ai_type</t>
+          <t>model_origin</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>MODERATOR_VARIABLES</t>
+          <t>CONSTRUCT_MAPPING</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -2273,241 +2299,249 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>generative, predictive, decision_support, conversational, robotic, general</t>
+          <t>TAM, UTAUT, UTAUT2, TPB, SCT, DOI, AI_specific, other</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>AI technology type</t>
+          <t>Theoretical origin of study construct</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>generative</t>
-        </is>
-      </c>
-      <c r="G57" s="3" t="inlineStr"/>
+          <t>TAM</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>education_level</t>
+          <t>reverse_coded</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>MODERATOR_VARIABLES</t>
+          <t>CONSTRUCT_MAPPING</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>categorical</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>K-12, undergraduate, graduate, vocational, mixed</t>
+          <t>TRUE, FALSE</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Education level</t>
+          <t>Whether sign was reversed</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>undergraduate</t>
-        </is>
-      </c>
-      <c r="G58" s="3" t="inlineStr"/>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>e.g., Complexity → EE (reverse)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>temporal_period</t>
+          <t>n_items</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>MODERATOR_VARIABLES</t>
+          <t>CONSTRUCT_MAPPING</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>categorical</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>pre_chatgpt (2022), post_chatgpt (2023-2026)</t>
+          <t>≥1</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Publication era</t>
+          <t>Number of items in scale</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>post_chatgpt</t>
-        </is>
-      </c>
-      <c r="G59" s="3" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>culture_cluster</t>
+          <t>scale_source</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>MODERATOR_VARIABLES</t>
+          <t>CONSTRUCT_MAPPING</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>categorical</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>individualist, collectivist</t>
+          <t>free text</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Hofstede-based culture type</t>
+          <t>Citation for scale</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>collectivist</t>
-        </is>
-      </c>
-      <c r="G60" s="3" t="inlineStr"/>
+          <t>Venkatesh et al. (2003)</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>sample_type</t>
+          <t>items_reviewed</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
+          <t>CONSTRUCT_MAPPING</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>TRUE, FALSE</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Whether items were reviewed for mapping</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>Required if confidence=moderate/low</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>— MODERATOR_VARIABLES —</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="n"/>
+      <c r="C62" s="2" t="n"/>
+      <c r="D62" s="2" t="n"/>
+      <c r="E62" s="2" t="n"/>
+      <c r="F62" s="2" t="n"/>
+      <c r="G62" s="2" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>study_id</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
           <t>MODERATOR_VARIABLES</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t>categorical</t>
-        </is>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>students, instructors, mixed, administrators</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="inlineStr">
-        <is>
-          <t>Respondent type</t>
-        </is>
-      </c>
-      <c r="F61" s="3" t="inlineStr">
-        <is>
-          <t>students</t>
-        </is>
-      </c>
-      <c r="G61" s="3" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>user_role</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>MODERATOR_VARIABLES</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>categorical</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>student, instructor, both</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="inlineStr">
-        <is>
-          <t>Primary user role studied</t>
-        </is>
-      </c>
-      <c r="F62" s="3" t="inlineStr">
-        <is>
-          <t>student</t>
-        </is>
-      </c>
-      <c r="G62" s="3" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>— AI_EXTRACTION_PROVENANCE —</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr"/>
-      <c r="C63" s="2" t="inlineStr"/>
-      <c r="D63" s="2" t="inlineStr"/>
-      <c r="E63" s="2" t="inlineStr"/>
-      <c r="F63" s="2" t="inlineStr"/>
-      <c r="G63" s="2" t="inlineStr"/>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>S###</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Links to STUDY_METADATA</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>S001</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>study_id</t>
+          <t>ai_type</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>AI_EXTRACTION_PROVENANCE</t>
+          <t>MODERATOR_VARIABLES</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>categorical</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>S###</t>
+          <t>generative, predictive, decision_support, conversational, robotic, general</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>Links to STUDY_METADATA</t>
+          <t>AI technology type</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>S001</t>
-        </is>
-      </c>
-      <c r="G64" s="3" t="inlineStr"/>
+          <t>generative</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>extraction_phase</t>
+          <t>education_level</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>AI_EXTRACTION_PROVENANCE</t>
+          <t>MODERATOR_VARIABLES</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -2517,198 +2551,170 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>metadata, correlation, construct_mapping</t>
+          <t>K-12, undergraduate, graduate, vocational, mixed</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Which phase of extraction</t>
+          <t>Education level</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>correlation</t>
-        </is>
-      </c>
-      <c r="G65" s="3" t="inlineStr"/>
+          <t>undergraduate</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>claude_raw_output</t>
+          <t>temporal_period</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>AI_EXTRACTION_PROVENANCE</t>
+          <t>MODERATOR_VARIABLES</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>categorical</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>JSON</t>
+          <t>pre_chatgpt (2022), post_chatgpt (2023-2026)</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>Raw Claude CLI output</t>
+          <t>Publication era</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>{...}</t>
-        </is>
-      </c>
-      <c r="G66" s="3" t="inlineStr">
-        <is>
-          <t>claude-sonnet-4-6</t>
-        </is>
-      </c>
+          <t>post_chatgpt</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>claude_timestamp</t>
+          <t>culture_cluster</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>AI_EXTRACTION_PROVENANCE</t>
+          <t>MODERATOR_VARIABLES</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>categorical</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>ISO 8601</t>
+          <t>individualist, collectivist</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>When Claude processed</t>
+          <t>Hofstede-based culture type</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01T10:30:00Z</t>
-        </is>
-      </c>
-      <c r="G67" s="3" t="inlineStr"/>
+          <t>collectivist</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>claude_confidence</t>
+          <t>sample_type</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>AI_EXTRACTION_PROVENANCE</t>
+          <t>MODERATOR_VARIABLES</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>categorical</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>students, instructors, mixed, administrators</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>Claude confidence score</t>
+          <t>Respondent type</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>0.95</t>
-        </is>
-      </c>
-      <c r="G68" s="3" t="inlineStr"/>
+          <t>students</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>gemini_raw_output</t>
+          <t>user_role</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>AI_EXTRACTION_PROVENANCE</t>
+          <t>MODERATOR_VARIABLES</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>categorical</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>JSON</t>
+          <t>student, instructor, both</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>Raw Gemini CLI output</t>
+          <t>Primary user role studied</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>{...}</t>
-        </is>
-      </c>
-      <c r="G69" s="3" t="inlineStr">
-        <is>
-          <t>gemini-2.5-flash</t>
-        </is>
-      </c>
+          <t>student</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t>gemini_timestamp</t>
-        </is>
-      </c>
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>AI_EXTRACTION_PROVENANCE</t>
-        </is>
-      </c>
-      <c r="C70" s="3" t="inlineStr">
-        <is>
-          <t>datetime</t>
-        </is>
-      </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t>ISO 8601</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="inlineStr">
-        <is>
-          <t>When Gemini processed</t>
-        </is>
-      </c>
-      <c r="F70" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-01T10:31:00Z</t>
-        </is>
-      </c>
-      <c r="G70" s="3" t="inlineStr"/>
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>— AI_EXTRACTION_PROVENANCE —</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="n"/>
+      <c r="C70" s="2" t="n"/>
+      <c r="D70" s="2" t="n"/>
+      <c r="E70" s="2" t="n"/>
+      <c r="F70" s="2" t="n"/>
+      <c r="G70" s="2" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>gemini_confidence</t>
+          <t>study_id</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -2718,30 +2724,30 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>S###</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>Gemini confidence score</t>
+          <t>Links to STUDY_METADATA</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="G71" s="3" t="inlineStr"/>
+          <t>S001</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>codex_raw_output</t>
+          <t>extraction_phase</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -2751,34 +2757,30 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>categorical</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>JSON</t>
+          <t>metadata, correlation, construct_mapping</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>Raw Codex CLI output</t>
+          <t>Which phase of extraction</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>{...}</t>
-        </is>
-      </c>
-      <c r="G72" s="3" t="inlineStr">
-        <is>
-          <t>Latest codex model</t>
-        </is>
-      </c>
+          <t>correlation</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>codex_timestamp</t>
+          <t>claude_raw_output</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -2788,30 +2790,34 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>ISO 8601</t>
+          <t>JSON</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>When Codex processed</t>
+          <t>Raw Claude CLI output</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01T10:32:00Z</t>
-        </is>
-      </c>
-      <c r="G73" s="3" t="inlineStr"/>
+          <t>{...}</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>codex_confidence</t>
+          <t>claude_timestamp</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -2821,30 +2827,30 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>ISO 8601</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>Codex confidence score</t>
+          <t>When Claude processed</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>0.90</t>
-        </is>
-      </c>
-      <c r="G74" s="3" t="inlineStr"/>
+          <t>2026-04-01T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>consensus_value</t>
+          <t>claude_confidence</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -2854,30 +2860,30 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>varies</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>Consensus result from 3 models</t>
+          <t>Claude confidence score</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>0.52</t>
-        </is>
-      </c>
-      <c r="G75" s="3" t="inlineStr"/>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>consensus_method</t>
+          <t>gemini_raw_output</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -2887,30 +2893,34 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>categorical</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>full_agreement, median, null</t>
+          <t>JSON</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>How consensus was reached</t>
+          <t>Raw Gemini CLI output</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>full_agreement</t>
-        </is>
-      </c>
-      <c r="G76" s="3" t="inlineStr"/>
+          <t>{...}</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>gemini-2.5-flash</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>consensus_confidence</t>
+          <t>gemini_timestamp</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -2920,30 +2930,30 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>categorical</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>high, moderate, low, null</t>
+          <t>ISO 8601</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>Consensus confidence level</t>
+          <t>When Gemini processed</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="G77" s="3" t="inlineStr"/>
+          <t>2026-04-01T10:31:00Z</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>human_verified</t>
+          <t>gemini_confidence</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -2953,30 +2963,30 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>TRUE, FALSE</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>Whether human verified this extraction</t>
+          <t>Gemini confidence score</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="G78" s="3" t="inlineStr"/>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>human_correction</t>
+          <t>codex_raw_output</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -2991,76 +3001,100 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>free text or NA</t>
+          <t>JSON</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>What human corrected if any</t>
+          <t>Raw Codex CLI output</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G79" s="3" t="inlineStr"/>
+          <t>{...}</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>Latest codex model</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>— DISCREPANCY_LOG —</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr"/>
-      <c r="C80" s="2" t="inlineStr"/>
-      <c r="D80" s="2" t="inlineStr"/>
-      <c r="E80" s="2" t="inlineStr"/>
-      <c r="F80" s="2" t="inlineStr"/>
-      <c r="G80" s="2" t="inlineStr"/>
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>codex_timestamp</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>AI_EXTRACTION_PROVENANCE</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>ISO 8601</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>When Codex processed</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01T10:32:00Z</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>study_id</t>
+          <t>codex_confidence</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>DISCREPANCY_LOG</t>
+          <t>AI_EXTRACTION_PROVENANCE</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>S###</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>Study where discrepancy occurred</t>
+          <t>Codex confidence score</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>S023</t>
-        </is>
-      </c>
-      <c r="G81" s="3" t="inlineStr"/>
+          <t>0.90</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>variable_name</t>
+          <t>consensus_value</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>DISCREPANCY_LOG</t>
+          <t>AI_EXTRACTION_PROVENANCE</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -3070,190 +3104,170 @@
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>free text</t>
+          <t>varies</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>Variable with disagreement</t>
+          <t>Consensus result from 3 models</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>PE_BI_r</t>
-        </is>
-      </c>
-      <c r="G82" s="3" t="inlineStr"/>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>coder1_value</t>
+          <t>consensus_method</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>DISCREPANCY_LOG</t>
+          <t>AI_EXTRACTION_PROVENANCE</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>categorical</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>varies</t>
+          <t>full_agreement, median, null</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>Value from coder 1 (R2)</t>
+          <t>How consensus was reached</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>0.52</t>
-        </is>
-      </c>
-      <c r="G83" s="3" t="inlineStr"/>
+          <t>full_agreement</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>coder2_value</t>
+          <t>consensus_confidence</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>DISCREPANCY_LOG</t>
+          <t>AI_EXTRACTION_PROVENANCE</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>categorical</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>varies</t>
+          <t>high, moderate, low, null</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>Value from coder 2 (R3)</t>
+          <t>Consensus confidence level</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>0.58</t>
-        </is>
-      </c>
-      <c r="G84" s="3" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>ai_consensus_value</t>
+          <t>human_verified</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>DISCREPANCY_LOG</t>
+          <t>AI_EXTRACTION_PROVENANCE</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>varies</t>
+          <t>TRUE, FALSE</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>AI consensus value if available</t>
+          <t>Whether human verified this extraction</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>0.52</t>
-        </is>
-      </c>
-      <c r="G85" s="3" t="inlineStr"/>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>discrepancy_type</t>
+          <t>human_correction</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>DISCREPANCY_LOG</t>
+          <t>AI_EXTRACTION_PROVENANCE</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>categorical</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>clerical, interpretive, substantive</t>
+          <t>free text or NA</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>Classification</t>
+          <t>What human corrected if any</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>clerical</t>
-        </is>
-      </c>
-      <c r="G86" s="3" t="inlineStr"/>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="3" t="inlineStr">
-        <is>
-          <t>magnitude</t>
-        </is>
-      </c>
-      <c r="B87" s="3" t="inlineStr">
-        <is>
-          <t>DISCREPANCY_LOG</t>
-        </is>
-      </c>
-      <c r="C87" s="3" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="D87" s="3" t="inlineStr">
-        <is>
-          <t>≥0 or NA</t>
-        </is>
-      </c>
-      <c r="E87" s="3" t="inlineStr">
-        <is>
-          <t>Quantitative difference for r values</t>
-        </is>
-      </c>
-      <c r="F87" s="3" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="G87" s="3" t="inlineStr"/>
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>— DISCREPANCY_LOG —</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="n"/>
+      <c r="C87" s="2" t="n"/>
+      <c r="D87" s="2" t="n"/>
+      <c r="E87" s="2" t="n"/>
+      <c r="F87" s="2" t="n"/>
+      <c r="G87" s="2" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>final_value</t>
+          <t>study_id</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -3268,25 +3282,25 @@
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>varies</t>
+          <t>S###</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>Resolved value</t>
+          <t>Study where discrepancy occurred</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>0.58</t>
-        </is>
-      </c>
-      <c r="G88" s="3" t="inlineStr"/>
+          <t>S023</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>resolution_method</t>
+          <t>variable_name</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -3296,30 +3310,30 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>categorical</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>consensus, pi_decision, source_verification</t>
+          <t>free text</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>How resolved</t>
+          <t>Variable with disagreement</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>source_verification</t>
-        </is>
-      </c>
-      <c r="G89" s="3" t="inlineStr"/>
+          <t>PE_BI_r</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>resolved_by</t>
+          <t>coder1_value</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -3334,25 +3348,29 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>initials</t>
+          <t>varies</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>Who made final decision</t>
+          <t>Value from primary coder (R1, R2, R3, or R4)</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>HY</t>
-        </is>
-      </c>
-      <c r="G90" s="3" t="inlineStr"/>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>Primary coder in the pair or single coder</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>resolution_date</t>
+          <t>coder2_value</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -3362,302 +3380,541 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>YYYY-MM-DD</t>
+          <t>varies</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>Date resolved</t>
+          <t>Value from secondary coder (Phase 1) or spot-checker (Phase 2)</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G91" s="3" t="inlineStr"/>
+          <t>0.58</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>Second coder within pair (Phase 1) or spot-checker (Phase 2)</t>
+        </is>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>— EXCLUSION_LOG —</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr"/>
-      <c r="C92" s="2" t="inlineStr"/>
-      <c r="D92" s="2" t="inlineStr"/>
-      <c r="E92" s="2" t="inlineStr"/>
-      <c r="F92" s="2" t="inlineStr"/>
-      <c r="G92" s="2" t="inlineStr"/>
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>ai_consensus_value</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>DISCREPANCY_LOG</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>varies</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>AI consensus value if available</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>study_id</t>
+          <t>discrepancy_type</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>EXCLUSION_LOG</t>
+          <t>DISCREPANCY_LOG</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>categorical</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>S###</t>
+          <t>clerical, interpretive, substantive</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>Study ID</t>
+          <t>Classification</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>S045</t>
-        </is>
-      </c>
-      <c r="G93" s="3" t="inlineStr"/>
+          <t>clerical</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>first_author</t>
+          <t>magnitude</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>EXCLUSION_LOG</t>
+          <t>DISCREPANCY_LOG</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>free text</t>
+          <t>≥0 or NA</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>First author</t>
+          <t>Quantitative difference for r values</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="G94" s="3" t="inlineStr"/>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>final_value</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>EXCLUSION_LOG</t>
+          <t>DISCREPANCY_LOG</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>2022-2026</t>
+          <t>varies</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>Publication year</t>
+          <t>Resolved value</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="G95" s="3" t="inlineStr"/>
+          <t>0.58</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>resolution_method</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>EXCLUSION_LOG</t>
+          <t>DISCREPANCY_LOG</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>categorical</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>free text</t>
+          <t>consensus, pi_decision, source_verification</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>Paper title</t>
+          <t>How resolved</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>AI Acceptance...</t>
-        </is>
-      </c>
-      <c r="G96" s="3" t="inlineStr"/>
+          <t>source_verification</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>exclusion_stage</t>
+          <t>resolved_by</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>EXCLUSION_LOG</t>
+          <t>DISCREPANCY_LOG</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>categorical</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>full_text, data_extraction</t>
+          <t>initials</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>When excluded</t>
+          <t>Who made final decision; uses cross-pair adjudication (Pair A discrepancies resolved by R3/R4, Pair B by R1/R2)</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>full_text</t>
-        </is>
-      </c>
-      <c r="G97" s="3" t="inlineStr"/>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>Cross-pair adjudication ensures independence of resolution</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>exclusion_code</t>
+          <t>resolution_date</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>EXCLUSION_LOG</t>
+          <t>DISCREPANCY_LOG</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>categorical</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>E1-E12, E-FT1-E-FT6</t>
+          <t>YYYY-MM-DD</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>Exclusion code</t>
+          <t>Date resolved</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>E-FT1</t>
-        </is>
-      </c>
-      <c r="G98" s="3" t="inlineStr"/>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="3" t="inlineStr">
-        <is>
-          <t>detailed_rationale</t>
-        </is>
-      </c>
-      <c r="B99" s="3" t="inlineStr">
-        <is>
-          <t>EXCLUSION_LOG</t>
-        </is>
-      </c>
-      <c r="C99" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D99" s="3" t="inlineStr">
-        <is>
-          <t>free text</t>
-        </is>
-      </c>
-      <c r="E99" s="3" t="inlineStr">
-        <is>
-          <t>Explanation</t>
-        </is>
-      </c>
-      <c r="F99" s="3" t="inlineStr">
-        <is>
-          <t>Only regression β, no correlation table</t>
-        </is>
-      </c>
-      <c r="G99" s="3" t="inlineStr"/>
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>— EXCLUSION_LOG —</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="n"/>
+      <c r="C99" s="2" t="n"/>
+      <c r="D99" s="2" t="n"/>
+      <c r="E99" s="2" t="n"/>
+      <c r="F99" s="2" t="n"/>
+      <c r="G99" s="2" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
+          <t>study_id</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>EXCLUSION_LOG</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>S###</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>Study ID</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>S045</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>first_author</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>EXCLUSION_LOG</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>free text</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>First author</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>EXCLUSION_LOG</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>2022-2026</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>Publication year</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>EXCLUSION_LOG</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>free text</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>Paper title</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>AI Acceptance...</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>exclusion_stage</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>EXCLUSION_LOG</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>full_text, data_extraction</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>When excluded</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>full_text</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>exclusion_code</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>EXCLUSION_LOG</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>E1-E12, E-FT1-E-FT6</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>Exclusion code</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>E-FT1</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>detailed_rationale</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>EXCLUSION_LOG</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>free text</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>Explanation</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>Only regression β, no correlation table</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
           <t>final_decision</t>
         </is>
       </c>
-      <c r="B100" s="3" t="inlineStr">
+      <c r="B107" s="3" t="inlineStr">
         <is>
           <t>EXCLUSION_LOG</t>
         </is>
       </c>
-      <c r="C100" s="3" t="inlineStr">
+      <c r="C107" s="3" t="inlineStr">
         <is>
           <t>categorical</t>
         </is>
       </c>
-      <c r="D100" s="3" t="inlineStr">
+      <c r="D107" s="3" t="inlineStr">
         <is>
           <t>exclude</t>
         </is>
       </c>
-      <c r="E100" s="3" t="inlineStr">
+      <c r="E107" s="3" t="inlineStr">
         <is>
           <t>Final decision</t>
         </is>
       </c>
-      <c r="F100" s="3" t="inlineStr">
+      <c r="F107" s="3" t="inlineStr">
         <is>
           <t>exclude</t>
         </is>
       </c>
-      <c r="G100" s="3" t="inlineStr"/>
+      <c r="G107" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3670,7 +3927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X1"/>
+  <dimension ref="A1:AD1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3697,6 +3954,12 @@
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="18" customWidth="1" min="25" max="25"/>
+    <col width="18" customWidth="1" min="26" max="26"/>
+    <col width="18" customWidth="1" min="27" max="27"/>
+    <col width="18" customWidth="1" min="28" max="28"/>
+    <col width="18" customWidth="1" min="29" max="29"/>
+    <col width="18" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -3820,9 +4083,39 @@
           <t>ai_precoded_verified</t>
         </is>
       </c>
+      <c r="Y1" s="6" t="inlineStr">
+        <is>
+          <t>coding_phase</t>
+        </is>
+      </c>
+      <c r="Z1" s="6" t="inlineStr">
+        <is>
+          <t>coder_pair</t>
+        </is>
+      </c>
+      <c r="AA1" s="6" t="inlineStr">
+        <is>
+          <t>primary_coder</t>
+        </is>
+      </c>
+      <c r="AB1" s="6" t="inlineStr">
+        <is>
+          <t>secondary_coder</t>
+        </is>
+      </c>
+      <c r="AC1" s="6" t="inlineStr">
+        <is>
+          <t>spot_checker</t>
+        </is>
+      </c>
+      <c r="AD1" s="6" t="inlineStr">
+        <is>
+          <t>adjudicator</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="8">
+  <dataValidations count="14">
     <dataValidation sqref="F2:F500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="Select publication type" type="list">
       <formula1>"journal,conference"</formula1>
     </dataValidation>
@@ -3846,6 +4139,24 @@
     </dataValidation>
     <dataValidation sqref="T2:T500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"addressed,not_addressed,partial"</formula1>
+    </dataValidation>
+    <dataValidation sqref="Y2:Y500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"calibration,phase1_dual,phase2_single"</formula1>
+    </dataValidation>
+    <dataValidation sqref="Z2:Z500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"pair_A,pair_B,NA"</formula1>
+    </dataValidation>
+    <dataValidation sqref="AA2:AA500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"R1,R2,R3,R4"</formula1>
+    </dataValidation>
+    <dataValidation sqref="AB2:AB500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"R1,R2,R3,R4,NA"</formula1>
+    </dataValidation>
+    <dataValidation sqref="AC2:AC500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"R1,R2,R3,R4,NA"</formula1>
+    </dataValidation>
+    <dataValidation sqref="AD2:AD500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"R1,R2,R3,R4,NA"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
